--- a/data/trans_orig/P2A_fisi_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_fisi_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2007</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad física en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8870</t>
+          <t>9696</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25337</t>
+          <t>26348</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18200</t>
+          <t>18189</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16440</t>
+          <t>17019</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37124</t>
+          <t>38261</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>448439</t>
+          <t>447428</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>464906</t>
+          <t>464080</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>288480</t>
+          <t>288491</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>301071</t>
+          <t>301202</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>743333</t>
+          <t>742196</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>764017</t>
+          <t>763438</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18616</t>
+          <t>18889</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9555</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26276</t>
+          <t>25394</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17490</t>
+          <t>17161</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38100</t>
+          <t>39624</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>348318</t>
+          <t>348045</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>362180</t>
+          <t>362067</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>345589</t>
+          <t>346471</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>362310</t>
+          <t>363387</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>700699</t>
+          <t>699175</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>721309</t>
+          <t>721638</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22338</t>
+          <t>21893</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43249</t>
+          <t>44522</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7518</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22899</t>
+          <t>22630</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34487</t>
+          <t>33077</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60192</t>
+          <t>60286</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>499140</t>
+          <t>497867</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520051</t>
+          <t>520496</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144883</t>
+          <t>145152</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160264</t>
+          <t>160269</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649979</t>
+          <t>649885</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>675684</t>
+          <t>677094</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62369</t>
+          <t>62747</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97669</t>
+          <t>96658</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33979</t>
+          <t>32961</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63920</t>
+          <t>61251</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104451</t>
+          <t>104011</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149633</t>
+          <t>146590</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1140665</t>
+          <t>1141676</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1175965</t>
+          <t>1175587</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>650365</t>
+          <t>653034</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>680306</t>
+          <t>681324</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1802987</t>
+          <t>1806030</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1848169</t>
+          <t>1848609</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13614</t>
+          <t>13793</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32161</t>
+          <t>35219</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31298</t>
+          <t>31036</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56897</t>
+          <t>56528</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50354</t>
+          <t>49290</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82671</t>
+          <t>84122</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>318394</t>
+          <t>315336</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>336941</t>
+          <t>336762</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>511855</t>
+          <t>512224</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>537454</t>
+          <t>537716</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>836636</t>
+          <t>835185</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>868953</t>
+          <t>870017</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13272</t>
+          <t>13235</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>64677</t>
+          <t>64240</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>102497</t>
+          <t>99552</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71599</t>
+          <t>72256</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>107838</t>
+          <t>107783</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>284929</t>
+          <t>284966</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>295544</t>
+          <t>296213</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1146263</t>
+          <t>1149208</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1184083</t>
+          <t>1184520</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1439122</t>
+          <t>1439177</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1475361</t>
+          <t>1474704</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>140338</t>
+          <t>140353</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>191001</t>
+          <t>188739</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>185848</t>
+          <t>183144</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>245617</t>
+          <t>241471</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>336574</t>
+          <t>337753</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>411677</t>
+          <t>413937</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3079189</t>
+          <t>3081451</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3129852</t>
+          <t>3129837</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3132507</t>
+          <t>3136653</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3192276</t>
+          <t>3194980</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6236637</t>
+          <t>6234377</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6311740</t>
+          <t>6310561</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,92%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2012</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad física en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11880</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34361</t>
+          <t>35792</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11181</t>
+          <t>10869</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28845</t>
+          <t>29248</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27235</t>
+          <t>26516</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54843</t>
+          <t>54170</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>402850</t>
+          <t>401419</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425331</t>
+          <t>424679</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>285609</t>
+          <t>285206</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>303273</t>
+          <t>303585</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>696822</t>
+          <t>697495</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>724430</t>
+          <t>725149</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14034</t>
+          <t>15041</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33794</t>
+          <t>34948</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13091</t>
+          <t>12259</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31883</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31331</t>
+          <t>30926</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59104</t>
+          <t>57826</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>385003</t>
+          <t>383849</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>404763</t>
+          <t>403756</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>306128</t>
+          <t>307036</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>324920</t>
+          <t>325752</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>697704</t>
+          <t>698982</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>725477</t>
+          <t>725882</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38128</t>
+          <t>38751</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67876</t>
+          <t>70676</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15011</t>
+          <t>14765</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33129</t>
+          <t>34759</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59845</t>
+          <t>59896</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96085</t>
+          <t>96306</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>561539</t>
+          <t>558739</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>591287</t>
+          <t>590664</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>227000</t>
+          <t>225370</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>245118</t>
+          <t>245364</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>793459</t>
+          <t>793238</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>829699</t>
+          <t>829648</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85967</t>
+          <t>87434</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130186</t>
+          <t>130156</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58480</t>
+          <t>58785</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92460</t>
+          <t>91599</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>155801</t>
+          <t>154842</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>209723</t>
+          <t>209123</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1028823</t>
+          <t>1028853</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1073042</t>
+          <t>1071575</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>674197</t>
+          <t>675058</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>708177</t>
+          <t>707872</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1715944</t>
+          <t>1716544</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1769866</t>
+          <t>1770825</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23527</t>
+          <t>25504</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47550</t>
+          <t>48841</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67460</t>
+          <t>67509</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>102558</t>
+          <t>104850</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>98887</t>
+          <t>101028</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142238</t>
+          <t>142813</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>463046</t>
+          <t>461755</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>487069</t>
+          <t>485092</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>658964</t>
+          <t>656672</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>694062</t>
+          <t>694013</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1129880</t>
+          <t>1129305</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1173231</t>
+          <t>1171090</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,06%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7018</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22084</t>
+          <t>22008</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,82 +5098,82 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>8,25%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>101242</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>82814</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>122887</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>9,13%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>7,47%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>11,08%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>113792</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>94176</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>135299</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
           <t>8,27%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>101242</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>81935</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>122198</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>9,13%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>7,39%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>11,02%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>113792</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>94696</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>138892</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244798</t>
+          <t>244874</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259864</t>
+          <t>260945</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,82 +5211,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>91,75%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>97,78%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1008109</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>986464</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1026537</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>90,87%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>88,92%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>92,53%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1262441</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>1240934</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>1282057</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>91,73%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>97,37%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>949</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1008109</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>987153</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1027416</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>90,87%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>88,98%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>92,61%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1262441</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>1237341</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1281537</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>91,73%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>222171</t>
+          <t>220259</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>286352</t>
+          <t>288435</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>289043</t>
+          <t>288331</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>357987</t>
+          <t>359445</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>531612</t>
+          <t>526199</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>623567</t>
+          <t>623504</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3135558</t>
+          <t>3133475</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3199739</t>
+          <t>3201651</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3192138</t>
+          <t>3190680</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3261082</t>
+          <t>3261794</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6348468</t>
+          <t>6348531</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6440423</t>
+          <t>6445836</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,45%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2016</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad física en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8812</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26450</t>
+          <t>25141</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8987</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21810</t>
+          <t>21695</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45793</t>
+          <t>44311</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>402642</t>
+          <t>403951</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>420280</t>
+          <t>420530</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>338458</t>
+          <t>338068</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>730354</t>
+          <t>731836</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>754337</t>
+          <t>754452</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10060</t>
+          <t>9826</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26376</t>
+          <t>25953</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6396</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22009</t>
+          <t>20807</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19161</t>
+          <t>18564</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42828</t>
+          <t>40972</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>350851</t>
+          <t>351274</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>367167</t>
+          <t>367401</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>350264</t>
+          <t>351466</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>365877</t>
+          <t>366537</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>706672</t>
+          <t>708528</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>730339</t>
+          <t>730936</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23232</t>
+          <t>22124</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46645</t>
+          <t>45569</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24333</t>
+          <t>23758</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34717</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61857</t>
+          <t>63208</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>475269</t>
+          <t>476345</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>498682</t>
+          <t>499790</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141790</t>
+          <t>142365</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158919</t>
+          <t>158897</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>626179</t>
+          <t>624828</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653319</t>
+          <t>653313</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56750</t>
+          <t>56151</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94304</t>
+          <t>90610</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44039</t>
+          <t>43925</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73564</t>
+          <t>72910</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110109</t>
+          <t>109274</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>154596</t>
+          <t>152747</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1055334</t>
+          <t>1059028</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1092888</t>
+          <t>1093487</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>752312</t>
+          <t>752966</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>781837</t>
+          <t>781951</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1820918</t>
+          <t>1822767</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1865405</t>
+          <t>1866240</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,47%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24392</t>
+          <t>23950</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48397</t>
+          <t>47848</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44772</t>
+          <t>45801</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76323</t>
+          <t>76035</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75244</t>
+          <t>74867</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114300</t>
+          <t>114769</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>572309</t>
+          <t>572858</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>596314</t>
+          <t>596756</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>661921</t>
+          <t>662209</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>693472</t>
+          <t>692443</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1244650</t>
+          <t>1244181</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1283706</t>
+          <t>1284083</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,49%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>8099</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23143</t>
+          <t>23572</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66797</t>
+          <t>67305</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>104647</t>
+          <t>104198</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80975</t>
+          <t>80822</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>120333</t>
+          <t>121688</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264002</t>
+          <t>263573</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>278981</t>
+          <t>279046</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>977378</t>
+          <t>977827</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1015228</t>
+          <t>1014720</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1248837</t>
+          <t>1247482</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1288195</t>
+          <t>1288348</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>162492</t>
+          <t>162917</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>216872</t>
+          <t>216339</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>211641</t>
+          <t>215465</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>277644</t>
+          <t>278505</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>394680</t>
+          <t>390427</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>476333</t>
+          <t>475250</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3168850</t>
+          <t>3169383</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3223230</t>
+          <t>3222805</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3253952</t>
+          <t>3253091</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3319955</t>
+          <t>3316131</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6440985</t>
+          <t>6442068</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6522638</t>
+          <t>6526891</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2023</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad física en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34612</t>
+          <t>34708</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61430</t>
+          <t>61951</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18855</t>
+          <t>19974</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35685</t>
+          <t>37111</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57855</t>
+          <t>57990</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90684</t>
+          <t>89633</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>443782</t>
+          <t>443261</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>470600</t>
+          <t>470504</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>411782</t>
+          <t>410356</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>428612</t>
+          <t>427493</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>861995</t>
+          <t>863046</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>894824</t>
+          <t>894689</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22196</t>
+          <t>21772</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44449</t>
+          <t>43630</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17630</t>
+          <t>18238</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33216</t>
+          <t>33661</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44662</t>
+          <t>45013</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71618</t>
+          <t>72595</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>407764</t>
+          <t>408583</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>430017</t>
+          <t>430441</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>349364</t>
+          <t>348919</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>364950</t>
+          <t>364342</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>763175</t>
+          <t>762198</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>790131</t>
+          <t>789780</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,61%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18523</t>
+          <t>20176</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91628</t>
+          <t>91903</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13559</t>
+          <t>13554</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28207</t>
+          <t>29382</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29358</t>
+          <t>29044</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110346</t>
+          <t>108941</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>576636</t>
+          <t>576361</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>649741</t>
+          <t>648088</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138704</t>
+          <t>137529</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153352</t>
+          <t>153357</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>724829</t>
+          <t>726234</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>805817</t>
+          <t>806131</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>108021</t>
+          <t>107231</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>150913</t>
+          <t>150457</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81349</t>
+          <t>82005</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>615058</t>
+          <t>550714</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>211337</t>
+          <t>210822</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>863044</t>
+          <t>934845</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>883906</t>
+          <t>884362</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>926798</t>
+          <t>927588</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>363036</t>
+          <t>427380</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>896745</t>
+          <t>896089</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1149868</t>
+          <t>1078067</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1801575</t>
+          <t>1802090</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,53%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65710</t>
+          <t>66951</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100020</t>
+          <t>100937</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81810</t>
+          <t>79101</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>128782</t>
+          <t>129087</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>156773</t>
+          <t>155791</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>219994</t>
+          <t>219937</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>375026</t>
+          <t>374109</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>409336</t>
+          <t>408095</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>712553</t>
+          <t>712248</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>759525</t>
+          <t>762234</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1096387</t>
+          <t>1096444</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1159608</t>
+          <t>1160590</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,17%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23575</t>
+          <t>25290</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>102260</t>
+          <t>102923</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>134521</t>
+          <t>134797</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>111067</t>
+          <t>110331</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>148664</t>
+          <t>148330</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>216932</t>
+          <t>215217</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235215</t>
+          <t>235086</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>626850</t>
+          <t>626574</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>659111</t>
+          <t>658448</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>853214</t>
+          <t>853548</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>890811</t>
+          <t>891547</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,99%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>277017</t>
+          <t>277271</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>399573</t>
+          <t>400281</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>374886</t>
+          <t>378579</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1150682</t>
+          <t>1140859</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>717501</t>
+          <t>719801</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1501352</t>
+          <t>1562265</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2976487</t>
+          <t>2975779</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3099043</t>
+          <t>3098789</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2427076</t>
+          <t>2436899</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3202872</t>
+          <t>3199179</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5452466</t>
+          <t>5391553</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6236317</t>
+          <t>6234017</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_fisi_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_fisi_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9696</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26348</t>
+          <t>26360</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18189</t>
+          <t>18553</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17019</t>
+          <t>17367</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38261</t>
+          <t>36864</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>447428</t>
+          <t>447416</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>464080</t>
+          <t>464717</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>288491</t>
+          <t>288127</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>301202</t>
+          <t>301437</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>742196</t>
+          <t>743593</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>763438</t>
+          <t>763090</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18889</t>
+          <t>19055</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>9644</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25394</t>
+          <t>26713</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17161</t>
+          <t>17450</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39624</t>
+          <t>40349</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>348045</t>
+          <t>347879</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>362067</t>
+          <t>362243</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>346471</t>
+          <t>345152</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363387</t>
+          <t>362221</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>699175</t>
+          <t>698450</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>721638</t>
+          <t>721349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21893</t>
+          <t>22601</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44522</t>
+          <t>43968</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22630</t>
+          <t>21870</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33077</t>
+          <t>33645</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60286</t>
+          <t>59708</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>497867</t>
+          <t>498421</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520496</t>
+          <t>519788</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145152</t>
+          <t>145912</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160269</t>
+          <t>160065</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649885</t>
+          <t>650463</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>677094</t>
+          <t>676526</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62747</t>
+          <t>62426</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96658</t>
+          <t>95510</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32961</t>
+          <t>35761</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61251</t>
+          <t>62608</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104011</t>
+          <t>105236</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>146590</t>
+          <t>148869</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1141676</t>
+          <t>1142824</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1175587</t>
+          <t>1175908</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>653034</t>
+          <t>651677</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>681324</t>
+          <t>678524</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1806030</t>
+          <t>1803751</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1848609</t>
+          <t>1847384</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,61%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13793</t>
+          <t>13970</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35219</t>
+          <t>33846</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31036</t>
+          <t>30431</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56528</t>
+          <t>55162</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49290</t>
+          <t>49815</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84122</t>
+          <t>82190</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>315336</t>
+          <t>316709</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>336762</t>
+          <t>336585</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>512224</t>
+          <t>513590</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>537716</t>
+          <t>538321</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>835185</t>
+          <t>837117</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>870017</t>
+          <t>869492</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>14583</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>64240</t>
+          <t>66529</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>99552</t>
+          <t>99455</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72256</t>
+          <t>71205</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>107783</t>
+          <t>107426</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>284966</t>
+          <t>283618</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>296213</t>
+          <t>295524</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1149208</t>
+          <t>1149305</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1184520</t>
+          <t>1182231</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1439177</t>
+          <t>1439534</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1474704</t>
+          <t>1475755</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>140353</t>
+          <t>138866</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>188739</t>
+          <t>187347</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>183144</t>
+          <t>183566</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>241471</t>
+          <t>242323</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>337753</t>
+          <t>337279</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>413937</t>
+          <t>414241</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3081451</t>
+          <t>3082843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3129837</t>
+          <t>3131324</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3136653</t>
+          <t>3135801</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3194980</t>
+          <t>3194558</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6234377</t>
+          <t>6234073</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6310561</t>
+          <t>6311035</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12532</t>
+          <t>12525</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35792</t>
+          <t>33751</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10869</t>
+          <t>11224</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29248</t>
+          <t>29965</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26516</t>
+          <t>26988</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54170</t>
+          <t>54414</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>401419</t>
+          <t>403460</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424679</t>
+          <t>424686</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>285206</t>
+          <t>284489</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>303585</t>
+          <t>303230</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>697495</t>
+          <t>697251</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>725149</t>
+          <t>724677</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15041</t>
+          <t>14065</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34948</t>
+          <t>34344</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12259</t>
+          <t>12204</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30975</t>
+          <t>31747</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30926</t>
+          <t>31269</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57826</t>
+          <t>58758</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>383849</t>
+          <t>384453</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>403756</t>
+          <t>404732</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>307036</t>
+          <t>306264</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>325752</t>
+          <t>325807</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>698982</t>
+          <t>698050</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>725882</t>
+          <t>725539</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,87%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38751</t>
+          <t>38735</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70676</t>
+          <t>69162</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14765</t>
+          <t>15540</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34759</t>
+          <t>34142</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59896</t>
+          <t>59172</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96306</t>
+          <t>94544</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>558739</t>
+          <t>560253</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>590664</t>
+          <t>590680</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>225370</t>
+          <t>225987</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>245364</t>
+          <t>244589</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>793238</t>
+          <t>795000</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>829648</t>
+          <t>830372</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87434</t>
+          <t>87875</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130156</t>
+          <t>128744</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58785</t>
+          <t>58551</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91599</t>
+          <t>92958</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>154842</t>
+          <t>154587</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>209123</t>
+          <t>212422</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1028853</t>
+          <t>1030265</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1071575</t>
+          <t>1071134</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>675058</t>
+          <t>673699</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>707872</t>
+          <t>708106</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1716544</t>
+          <t>1713245</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1770825</t>
+          <t>1771080</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25504</t>
+          <t>25815</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48841</t>
+          <t>48434</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67509</t>
+          <t>67274</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>104850</t>
+          <t>103888</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101028</t>
+          <t>100351</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142813</t>
+          <t>144720</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>461755</t>
+          <t>462162</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>485092</t>
+          <t>484781</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>656672</t>
+          <t>657634</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>694013</t>
+          <t>694248</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1129305</t>
+          <t>1127398</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1171090</t>
+          <t>1171767</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5937</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22008</t>
+          <t>21051</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>82814</t>
+          <t>83630</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>122887</t>
+          <t>122050</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>94176</t>
+          <t>92804</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>135299</t>
+          <t>133700</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244874</t>
+          <t>245831</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260945</t>
+          <t>261054</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>986464</t>
+          <t>987301</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1026537</t>
+          <t>1025721</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1240934</t>
+          <t>1242533</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1282057</t>
+          <t>1283429</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>220259</t>
+          <t>219046</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>288435</t>
+          <t>282462</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>288331</t>
+          <t>289643</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>359445</t>
+          <t>360784</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>526199</t>
+          <t>531077</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>623504</t>
+          <t>620498</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3133475</t>
+          <t>3139448</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3201651</t>
+          <t>3202864</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3190680</t>
+          <t>3189341</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3261794</t>
+          <t>3260482</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6348531</t>
+          <t>6351537</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6445836</t>
+          <t>6440958</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,38%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>9573</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25141</t>
+          <t>26786</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8987</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26429</t>
+          <t>26804</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21695</t>
+          <t>21640</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44311</t>
+          <t>45722</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>403951</t>
+          <t>402306</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>420530</t>
+          <t>419519</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>320626</t>
+          <t>320251</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>338068</t>
+          <t>337540</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>731836</t>
+          <t>730425</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>754452</t>
+          <t>754507</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9826</t>
+          <t>10577</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25953</t>
+          <t>26780</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5736</t>
+          <t>5467</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20807</t>
+          <t>21374</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,47 +6396,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
+          <t>5,74%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>28543</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>19259</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>41933</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>5,59%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>28543</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>18564</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>40972</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>351274</t>
+          <t>350447</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>367401</t>
+          <t>366650</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>351466</t>
+          <t>350899</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>366537</t>
+          <t>366806</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,47 +6509,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>94,26%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>720957</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>707567</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>730241</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>96,19%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>94,41%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>720957</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>708528</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>730936</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>96,19%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>94,53%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22124</t>
+          <t>23869</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45569</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23758</t>
+          <t>23003</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34723</t>
+          <t>35055</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63208</t>
+          <t>61562</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>476345</t>
+          <t>476114</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>499790</t>
+          <t>498045</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142365</t>
+          <t>143120</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158897</t>
+          <t>158834</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>624828</t>
+          <t>626474</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653313</t>
+          <t>652981</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56151</t>
+          <t>56808</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90610</t>
+          <t>92409</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43925</t>
+          <t>44029</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72910</t>
+          <t>75115</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>109274</t>
+          <t>108858</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>152747</t>
+          <t>153905</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1059028</t>
+          <t>1057229</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1093487</t>
+          <t>1092830</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>752966</t>
+          <t>750761</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>781951</t>
+          <t>781847</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1822767</t>
+          <t>1821609</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1866240</t>
+          <t>1866656</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,49%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23950</t>
+          <t>24145</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47848</t>
+          <t>48953</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45801</t>
+          <t>45151</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76035</t>
+          <t>77223</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74867</t>
+          <t>76351</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114769</t>
+          <t>116341</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>572858</t>
+          <t>571753</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>596756</t>
+          <t>596561</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>662209</t>
+          <t>661021</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>692443</t>
+          <t>693093</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1244181</t>
+          <t>1242609</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1284083</t>
+          <t>1282599</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>8862</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23572</t>
+          <t>23345</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67305</t>
+          <t>68309</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>104198</t>
+          <t>105329</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80822</t>
+          <t>81168</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>121688</t>
+          <t>120704</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>263573</t>
+          <t>263800</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>279046</t>
+          <t>278283</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>977827</t>
+          <t>976696</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1014720</t>
+          <t>1013716</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1247482</t>
+          <t>1248466</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1288348</t>
+          <t>1288002</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,07%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>162917</t>
+          <t>162590</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>216339</t>
+          <t>215214</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>215465</t>
+          <t>215057</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>278505</t>
+          <t>279164</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>390427</t>
+          <t>390109</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>475250</t>
+          <t>471588</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3169383</t>
+          <t>3170508</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3222805</t>
+          <t>3223132</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3253091</t>
+          <t>3252432</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3316131</t>
+          <t>3316539</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6442068</t>
+          <t>6445730</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6526891</t>
+          <t>6527209</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>45557</t>
+          <t>47362</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34708</t>
+          <t>36059</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61951</t>
+          <t>63963</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,17 +8668,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26331</t>
+          <t>28701</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19974</t>
+          <t>20746</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37111</t>
+          <t>38465</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>71888</t>
+          <t>76063</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57990</t>
+          <t>61006</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89633</t>
+          <t>92551</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>459655</t>
+          <t>503256</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>443261</t>
+          <t>486655</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>470504</t>
+          <t>514559</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,17 +8781,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>421136</t>
+          <t>459710</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>410356</t>
+          <t>449946</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>427493</t>
+          <t>467665</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>880791</t>
+          <t>962966</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>863046</t>
+          <t>946478</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>894689</t>
+          <t>978023</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,13%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31916</t>
+          <t>33772</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21772</t>
+          <t>23804</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43630</t>
+          <t>47353</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24851</t>
+          <t>28051</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18238</t>
+          <t>20308</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33661</t>
+          <t>37498</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>56767</t>
+          <t>61824</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45013</t>
+          <t>48596</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72595</t>
+          <t>78762</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>420297</t>
+          <t>449440</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>408583</t>
+          <t>435859</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>430441</t>
+          <t>459408</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>357729</t>
+          <t>395092</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>348919</t>
+          <t>385645</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>364342</t>
+          <t>402835</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>778026</t>
+          <t>844531</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>762198</t>
+          <t>827593</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>789780</t>
+          <t>857759</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>53832</t>
+          <t>57259</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20176</t>
+          <t>44937</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91903</t>
+          <t>71947</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19767</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13554</t>
+          <t>15353</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29382</t>
+          <t>33066</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>73599</t>
+          <t>79723</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29044</t>
+          <t>64633</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108941</t>
+          <t>99591</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>614432</t>
+          <t>414353</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>576361</t>
+          <t>399665</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>648088</t>
+          <t>426675</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>147144</t>
+          <t>165033</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137529</t>
+          <t>154431</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153357</t>
+          <t>172144</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>761576</t>
+          <t>579386</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>726234</t>
+          <t>559518</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>806131</t>
+          <t>594476</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>90,19%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>127917</t>
+          <t>138618</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>107231</t>
+          <t>116883</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>150457</t>
+          <t>159891</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>273853</t>
+          <t>79216</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82005</t>
+          <t>65961</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>550714</t>
+          <t>93723</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>401770</t>
+          <t>217834</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>210822</t>
+          <t>191789</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>934845</t>
+          <t>245720</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>906902</t>
+          <t>993225</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>884362</t>
+          <t>971952</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>927588</t>
+          <t>1014960</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>704241</t>
+          <t>781995</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>427380</t>
+          <t>767488</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>896089</t>
+          <t>795250</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1611142</t>
+          <t>1775220</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1078067</t>
+          <t>1747334</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1802090</t>
+          <t>1801265</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>90,38%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>82188</t>
+          <t>85679</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66951</t>
+          <t>69600</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100937</t>
+          <t>106230</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>109220</t>
+          <t>125041</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>79101</t>
+          <t>110787</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>129087</t>
+          <t>142452</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>191408</t>
+          <t>210720</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>155791</t>
+          <t>188348</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>219937</t>
+          <t>236650</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>392858</t>
+          <t>482285</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>374109</t>
+          <t>461734</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>408095</t>
+          <t>498364</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>732115</t>
+          <t>705809</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>712248</t>
+          <t>688398</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>762234</t>
+          <t>720063</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1124973</t>
+          <t>1188094</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1096444</t>
+          <t>1162164</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1160590</t>
+          <t>1210466</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>86,54%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12007</t>
+          <t>11944</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25290</t>
+          <t>24978</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>117738</t>
+          <t>127029</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>102923</t>
+          <t>109418</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>134797</t>
+          <t>145616</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>129745</t>
+          <t>138973</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>110331</t>
+          <t>119186</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>148330</t>
+          <t>160927</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>228500</t>
+          <t>225284</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>215217</t>
+          <t>212250</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235086</t>
+          <t>231285</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>643633</t>
+          <t>717252</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>626574</t>
+          <t>698665</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>658448</t>
+          <t>734863</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>872133</t>
+          <t>942536</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>853548</t>
+          <t>920582</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>891547</t>
+          <t>962323</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,98%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,102 +10691,102 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>353417</t>
+          <t>374634</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>277271</t>
+          <t>336489</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>400281</t>
+          <t>410672</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>11,93%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>410503</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>381446</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>442338</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>11,29%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>10,49%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>12,17%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>785137</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>737763</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>839328</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>11,09%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>10,42%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>11,86%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>571760</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>378579</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>1140859</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>15,98%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>10,58%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>31,89%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>925176</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>719801</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1562265</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>13,3%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>10,35%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -10804,102 +10804,102 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3022643</t>
+          <t>3067842</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2975779</t>
+          <t>3031804</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3098789</t>
+          <t>3105987</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>88,07%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>90,23%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>4578</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3224890</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>3193055</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3253947</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>88,71%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>87,83%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>89,51%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>7463</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>6292732</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6238541</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6340106</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>88,91%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>88,14%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>91,79%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>4578</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>3005998</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>2436899</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>3199179</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>84,02%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>68,11%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>89,42%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>7463</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>6028642</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>5391553</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>6234017</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>86,7%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>77,53%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_fisi_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_fisi_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad física en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad física en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad física en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad física en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
